--- a/helper_tools/Workload Seeder.xlsx
+++ b/helper_tools/Workload Seeder.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/mohamed_mitkees_oracle_com/Documents/SalesAPP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/mohamed_mitkees_oracle_com/Documents/SalesAPP/helper_tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{CB7DE02C-0636-E94C-93FF-F9FC079531BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CA5C64E-AA11-D94F-B2F7-A32BA1F81D5E}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{CB7DE02C-0636-E94C-93FF-F9FC079531BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A0F74B-09A0-794C-8BE1-91ADE0433FA0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="148">
   <si>
     <t>Forecast type</t>
   </si>
@@ -118,15 +118,6 @@
     <t>Stitch</t>
   </si>
   <si>
-    <t xml:space="preserve">$-   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $-   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,000 </t>
-  </si>
-  <si>
     <t>A8N7FY</t>
   </si>
   <si>
@@ -139,12 +130,6 @@
     <t xml:space="preserve">TechOrbit /Etronix </t>
   </si>
   <si>
-    <t xml:space="preserve"> $100 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $200 </t>
-  </si>
-  <si>
     <t>A8N9XY</t>
   </si>
   <si>
@@ -154,12 +139,6 @@
     <t>LEELA MEGH Exchange LLC</t>
   </si>
   <si>
-    <t xml:space="preserve">$600 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $600 </t>
-  </si>
-  <si>
     <t>Purushothaman N.</t>
   </si>
   <si>
@@ -172,15 +151,6 @@
     <t>Thrifty</t>
   </si>
   <si>
-    <t xml:space="preserve">$475 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $708 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,891 </t>
-  </si>
-  <si>
     <t>A8N352</t>
   </si>
   <si>
@@ -193,12 +163,6 @@
     <t>Diamond Lease</t>
   </si>
   <si>
-    <t xml:space="preserve">$2,000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $2,000 </t>
-  </si>
-  <si>
     <t>Friday, October 24, 2025</t>
   </si>
   <si>
@@ -208,15 +172,6 @@
     <t>Dotcom</t>
   </si>
   <si>
-    <t xml:space="preserve"> $824 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $3,390 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $4,214 </t>
-  </si>
-  <si>
     <t>A88TB4</t>
   </si>
   <si>
@@ -226,21 +181,12 @@
     <t>Non-Reportable WL</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,769 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,769 </t>
-  </si>
-  <si>
     <t>Doc understanding</t>
   </si>
   <si>
     <t>Halsimplify</t>
   </si>
   <si>
-    <t xml:space="preserve">$100 </t>
-  </si>
-  <si>
     <t>Friday, September 26, 2025</t>
   </si>
   <si>
@@ -250,15 +196,6 @@
     <t>PointMatrix</t>
   </si>
   <si>
-    <t xml:space="preserve">$151 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,400 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,551 </t>
-  </si>
-  <si>
     <t xml:space="preserve">A8XB8Z </t>
   </si>
   <si>
@@ -268,21 +205,12 @@
     <t xml:space="preserve">IO Health </t>
   </si>
   <si>
-    <t xml:space="preserve"> $850 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,700 </t>
-  </si>
-  <si>
     <t>Monday, September 8, 2025</t>
   </si>
   <si>
     <t>Forfieted - Started Thursday for test workload</t>
   </si>
   <si>
-    <t xml:space="preserve"> $1,200 </t>
-  </si>
-  <si>
     <t>A8WVFX</t>
   </si>
   <si>
@@ -301,48 +229,27 @@
     <t xml:space="preserve">HA for their current application additional OCI infra expansion of 11K </t>
   </si>
   <si>
-    <t xml:space="preserve">$850 </t>
-  </si>
-  <si>
     <t>Won part of the IO Health WL</t>
   </si>
   <si>
     <t>Medical Consulation LLC</t>
   </si>
   <si>
-    <t xml:space="preserve"> $6,000 </t>
-  </si>
-  <si>
     <t>Pure IaaS for an ISV application. Medical prescriptions. Started Friday, will mark it as won</t>
   </si>
   <si>
     <t>Toothpick</t>
   </si>
   <si>
-    <t xml:space="preserve">$120 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $120 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $360 </t>
-  </si>
-  <si>
     <t>A8NPFZ</t>
   </si>
   <si>
     <t>Friday, September 19, 2025</t>
   </si>
   <si>
-    <t>They will expand their ops in UK.-Won $120/Month</t>
-  </si>
-  <si>
     <t>Gate Hills</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,000 </t>
-  </si>
-  <si>
     <t>Thursday, October 2, 2025</t>
   </si>
   <si>
@@ -352,15 +259,6 @@
     <t>Americana - Food</t>
   </si>
   <si>
-    <t xml:space="preserve">$2,500 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $3,000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $8,500 </t>
-  </si>
-  <si>
     <t>Thursday, September 11, 2025</t>
   </si>
   <si>
@@ -385,12 +283,6 @@
     <t>Gulftainer</t>
   </si>
   <si>
-    <t xml:space="preserve">$840 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $840 </t>
-  </si>
-  <si>
     <t>Existing contract</t>
   </si>
   <si>
@@ -403,12 +295,6 @@
     <t>CNTXT</t>
   </si>
   <si>
-    <t xml:space="preserve">$10,000 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $10,000 </t>
-  </si>
-  <si>
     <t>A8N7HQ</t>
   </si>
   <si>
@@ -424,15 +310,6 @@
     <t>Tamkeen</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,972 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,972 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $3,944 </t>
-  </si>
-  <si>
     <t>Strong 80%</t>
   </si>
   <si>
@@ -442,30 +319,15 @@
     <t>OIC</t>
   </si>
   <si>
-    <t xml:space="preserve"> $500 </t>
-  </si>
-  <si>
     <t>Wednesday, November 5, 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Forfieted - Container services </t>
   </si>
   <si>
-    <t xml:space="preserve">$300 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $300 </t>
-  </si>
-  <si>
     <t>VirtueMobility</t>
   </si>
   <si>
-    <t xml:space="preserve">$50 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $50 </t>
-  </si>
-  <si>
     <t xml:space="preserve">A8WXCW </t>
   </si>
   <si>
@@ -475,12 +337,6 @@
     <t>Info IDD</t>
   </si>
   <si>
-    <t xml:space="preserve"> $1,100 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $3,200 </t>
-  </si>
-  <si>
     <t>Tuesday, September 9, 2025</t>
   </si>
   <si>
@@ -490,9 +346,6 @@
     <t>Dijlah Gold</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,100 </t>
-  </si>
-  <si>
     <t>A8H37W</t>
   </si>
   <si>
@@ -502,12 +355,6 @@
     <t>Africa Institute</t>
   </si>
   <si>
-    <t xml:space="preserve">$3,300 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $3,300 </t>
-  </si>
-  <si>
     <t>A8SJS4</t>
   </si>
   <si>
@@ -520,12 +367,6 @@
     <t>Jadeed</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,600 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,600 </t>
-  </si>
-  <si>
     <t>A8VBQ4</t>
   </si>
   <si>
@@ -535,12 +376,6 @@
     <t>Afrozone</t>
   </si>
   <si>
-    <t xml:space="preserve"> $1,500 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $4,000 </t>
-  </si>
-  <si>
     <t>Monday 6th of OCtober, 2025</t>
   </si>
   <si>
@@ -559,12 +394,6 @@
     <t>Evollabs</t>
   </si>
   <si>
-    <t xml:space="preserve">$30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $30 </t>
-  </si>
-  <si>
     <t>A8YFJD</t>
   </si>
   <si>
@@ -574,18 +403,9 @@
     <t>Affinsys</t>
   </si>
   <si>
-    <t xml:space="preserve"> $900 </t>
-  </si>
-  <si>
     <t>Depa</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,875 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $1,875 </t>
-  </si>
-  <si>
     <t>A8WKNZ</t>
   </si>
   <si>
@@ -595,12 +415,6 @@
     <t>EBS L&amp;S</t>
   </si>
   <si>
-    <t xml:space="preserve">$330 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $330 </t>
-  </si>
-  <si>
     <t>A8ZJVW</t>
   </si>
   <si>
@@ -610,12 +424,6 @@
     <t>Moalajah</t>
   </si>
   <si>
-    <t xml:space="preserve">$390 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $390 </t>
-  </si>
-  <si>
     <t>A8ZJW9</t>
   </si>
   <si>
@@ -631,12 +439,6 @@
     <t>Tuesday, November 11, 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">$119 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> $119 </t>
-  </si>
-  <si>
     <t>A924ZX</t>
   </si>
   <si>
@@ -653,6 +455,15 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -   </t>
+  </si>
+  <si>
+    <t>They will expand their ops in UK.-Won 120/Month</t>
   </si>
 </sst>
 </file>
@@ -817,7 +628,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -892,6 +703,18 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1129,13 +952,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>208</v>
+        <v>142</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="H1" s="26" t="s">
         <v>4</v>
@@ -1159,7 +982,7 @@
         <v>10</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>210</v>
+        <v>144</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -1194,16 +1017,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>146</v>
+      </c>
+      <c r="G2" s="28">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="28">
+        <v>1000</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>25</v>
@@ -1215,13 +1038,13 @@
         <v>16</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -1248,7 +1071,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -1257,16 +1080,16 @@
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>40</v>
+        <v>145</v>
+      </c>
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2">
+        <v>200</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>23</v>
@@ -1278,11 +1101,11 @@
         <v>16</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
@@ -1309,7 +1132,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>21</v>
@@ -1319,14 +1142,14 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>45</v>
+      <c r="G4" s="2">
+        <v>600</v>
+      </c>
+      <c r="H4" s="2">
+        <v>600</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -1336,10 +1159,10 @@
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O4" s="16"/>
       <c r="P4" s="16"/>
@@ -1366,7 +1189,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -1374,17 +1197,17 @@
       <c r="D5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>52</v>
+      <c r="E5" s="2">
+        <v>475</v>
+      </c>
+      <c r="F5" s="2">
+        <v>708</v>
+      </c>
+      <c r="G5" s="2">
+        <v>708</v>
+      </c>
+      <c r="H5" s="28">
+        <v>1891</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>30</v>
@@ -1396,13 +1219,13 @@
         <v>16</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
@@ -1429,7 +1252,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>21</v>
@@ -1439,14 +1262,14 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>58</v>
+      <c r="G6" s="28">
+        <v>2000</v>
+      </c>
+      <c r="H6" s="28">
+        <v>2000</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>19</v>
@@ -1456,10 +1279,10 @@
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
@@ -1486,7 +1309,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -1495,16 +1318,16 @@
         <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>64</v>
+        <v>145</v>
+      </c>
+      <c r="F7" s="2">
+        <v>824</v>
+      </c>
+      <c r="G7" s="28">
+        <v>3390</v>
+      </c>
+      <c r="H7" s="28">
+        <v>4214</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
@@ -1516,13 +1339,13 @@
         <v>16</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
@@ -1549,21 +1372,21 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
-      <c r="G8" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>69</v>
+      <c r="G8" s="29">
+        <v>1769</v>
+      </c>
+      <c r="H8" s="29">
+        <v>1769</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>30</v>
@@ -1573,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="L8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
@@ -1606,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>12</v>
@@ -1616,14 +1439,14 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="G9" s="2">
+        <v>100</v>
+      </c>
+      <c r="H9" s="2">
+        <v>100</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -1633,10 +1456,10 @@
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
@@ -1663,7 +1486,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -1672,14 +1495,14 @@
         <v>13</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>78</v>
+      <c r="F10" s="2">
+        <v>151</v>
+      </c>
+      <c r="G10" s="30">
+        <v>1400</v>
+      </c>
+      <c r="H10" s="30">
+        <v>1551</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>28</v>
@@ -1691,10 +1514,10 @@
         <v>16</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>11</v>
@@ -1724,7 +1547,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>21</v>
@@ -1733,16 +1556,16 @@
         <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>83</v>
+        <v>145</v>
+      </c>
+      <c r="F11" s="2">
+        <v>850</v>
+      </c>
+      <c r="G11" s="2">
+        <v>850</v>
+      </c>
+      <c r="H11" s="28">
+        <v>1700</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>14</v>
@@ -1755,10 +1578,10 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
@@ -1794,16 +1617,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>86</v>
+        <v>146</v>
+      </c>
+      <c r="G12" s="28">
+        <v>1200</v>
+      </c>
+      <c r="H12" s="28">
+        <v>1200</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>23</v>
@@ -1815,13 +1638,13 @@
         <v>16</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" s="16"/>
@@ -1848,7 +1671,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>21</v>
@@ -1857,14 +1680,14 @@
         <v>13</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>40</v>
+      <c r="F13" s="2">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2">
+        <v>200</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>28</v>
@@ -1876,13 +1699,13 @@
         <v>16</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="O13" s="16"/>
       <c r="P13" s="16"/>
@@ -1913,7 +1736,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>21</v>
@@ -1921,17 +1744,17 @@
       <c r="D14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>93</v>
+      <c r="E14" s="2">
+        <v>850</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>82</v>
+        <v>146</v>
+      </c>
+      <c r="H14" s="2">
+        <v>850</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>14</v>
@@ -1944,10 +1767,10 @@
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
@@ -1974,7 +1797,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>12</v>
@@ -1982,17 +1805,17 @@
       <c r="D15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>96</v>
+      <c r="E15" s="28">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="28">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="28">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="28">
+        <v>6000</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>14</v>
@@ -2005,10 +1828,10 @@
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
@@ -2035,7 +1858,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>21</v>
@@ -2043,17 +1866,17 @@
       <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>101</v>
+      <c r="E16" s="2">
+        <v>120</v>
+      </c>
+      <c r="F16" s="2">
+        <v>120</v>
+      </c>
+      <c r="G16" s="2">
+        <v>120</v>
+      </c>
+      <c r="H16" s="2">
+        <v>360</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>25</v>
@@ -2065,13 +1888,13 @@
         <v>16</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
@@ -2098,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
@@ -2107,14 +1930,14 @@
         <v>13</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>58</v>
+      <c r="F17" s="28">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="28">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="28">
+        <v>2000</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>14</v>
@@ -2127,10 +1950,10 @@
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" s="16"/>
@@ -2157,7 +1980,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>21</v>
@@ -2165,17 +1988,17 @@
       <c r="D18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>112</v>
+      <c r="E18" s="28">
+        <v>2500</v>
+      </c>
+      <c r="F18" s="28">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="28">
+        <v>3000</v>
+      </c>
+      <c r="H18" s="28">
+        <v>8500</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>14</v>
@@ -2188,10 +2011,10 @@
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" s="16"/>
@@ -2224,7 +2047,7 @@
         <v>20</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>12</v>
@@ -2234,29 +2057,29 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>34</v>
+      <c r="G19" s="30">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="30">
+        <v>1000</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>16</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="O19" s="24"/>
       <c r="P19" s="16"/>
@@ -2283,7 +2106,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>21</v>
@@ -2293,11 +2116,11 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>122</v>
+      <c r="G20" s="2">
+        <v>840</v>
+      </c>
+      <c r="H20" s="2">
+        <v>840</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>30</v>
@@ -2309,13 +2132,13 @@
         <v>16</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" s="16"/>
@@ -2342,7 +2165,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>12</v>
@@ -2351,12 +2174,12 @@
         <v>26</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>127</v>
+      <c r="F21" s="28">
+        <v>10000</v>
       </c>
       <c r="G21" s="2"/>
-      <c r="H21" s="2" t="s">
-        <v>128</v>
+      <c r="H21" s="28">
+        <v>10000</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>18</v>
@@ -2368,7 +2191,7 @@
         <v>16</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="2"/>
@@ -2397,7 +2220,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>12</v>
@@ -2406,14 +2229,14 @@
         <v>13</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>45</v>
+      <c r="G22" s="2">
+        <v>600</v>
+      </c>
+      <c r="H22" s="2">
+        <v>600</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>18</v>
@@ -2425,11 +2248,11 @@
         <v>16</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="M22" s="12"/>
       <c r="N22" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
@@ -2456,39 +2279,39 @@
         <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>136</v>
+      <c r="F23" s="29">
+        <v>1972</v>
+      </c>
+      <c r="G23" s="29">
+        <v>1972</v>
+      </c>
+      <c r="H23" s="29">
+        <v>3944</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>16</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="M23" s="14"/>
       <c r="N23" s="6" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" s="16"/>
@@ -2515,7 +2338,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>21</v>
@@ -2524,14 +2347,14 @@
         <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>140</v>
+      <c r="G24" s="2">
+        <v>500</v>
+      </c>
+      <c r="H24" s="2">
+        <v>500</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>14</v>
@@ -2544,10 +2367,10 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="O24" s="16"/>
       <c r="P24" s="16"/>
@@ -2574,7 +2397,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>21</v>
@@ -2582,13 +2405,13 @@
       <c r="D25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>143</v>
+      <c r="E25" s="2">
+        <v>300</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2" t="s">
-        <v>144</v>
+      <c r="H25" s="2">
+        <v>300</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>28</v>
@@ -2600,13 +2423,13 @@
         <v>16</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
@@ -2633,7 +2456,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>12</v>
@@ -2643,11 +2466,11 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>147</v>
+      <c r="G26" s="9">
+        <v>50</v>
+      </c>
+      <c r="H26" s="9">
+        <v>50</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>28</v>
@@ -2659,10 +2482,10 @@
         <v>16</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="24"/>
@@ -2690,7 +2513,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>21</v>
@@ -2698,17 +2521,17 @@
       <c r="D27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>152</v>
+      <c r="E27" s="28">
+        <v>1000</v>
+      </c>
+      <c r="F27" s="28">
+        <v>1100</v>
+      </c>
+      <c r="G27" s="28">
+        <v>1100</v>
+      </c>
+      <c r="H27" s="28">
+        <v>3200</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>14</v>
@@ -2721,10 +2544,10 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>153</v>
+        <v>105</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="O27" s="16"/>
       <c r="P27" s="16"/>
@@ -2755,7 +2578,7 @@
         <v>17</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>12</v>
@@ -2765,11 +2588,11 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>151</v>
+      <c r="G28" s="30">
+        <v>1100</v>
+      </c>
+      <c r="H28" s="30">
+        <v>1100</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>28</v>
@@ -2781,13 +2604,13 @@
         <v>16</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="O28" s="24"/>
       <c r="P28" s="16"/>
@@ -2814,7 +2637,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>21</v>
@@ -2822,17 +2645,17 @@
       <c r="D29" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>160</v>
+      <c r="E29" s="28">
+        <v>3300</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>161</v>
+        <v>146</v>
+      </c>
+      <c r="H29" s="30">
+        <v>3300</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>28</v>
@@ -2844,13 +2667,13 @@
         <v>16</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
@@ -2877,7 +2700,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>21</v>
@@ -2885,13 +2708,13 @@
       <c r="D30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>166</v>
+      <c r="E30" s="28">
+        <v>1600</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="9"/>
-      <c r="H30" s="9" t="s">
-        <v>167</v>
+      <c r="H30" s="30">
+        <v>1600</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>28</v>
@@ -2903,11 +2726,11 @@
         <v>16</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="2" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
@@ -2934,7 +2757,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>12</v>
@@ -2942,17 +2765,17 @@
       <c r="D31" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>172</v>
+      <c r="E31" s="28">
+        <v>1000</v>
+      </c>
+      <c r="F31" s="28">
+        <v>1500</v>
+      </c>
+      <c r="G31" s="28">
+        <v>1500</v>
+      </c>
+      <c r="H31" s="28">
+        <v>4000</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>14</v>
@@ -2965,10 +2788,10 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="16" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="N31" s="16" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
@@ -2995,7 +2818,7 @@
         <v>20</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>12</v>
@@ -3005,11 +2828,11 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>39</v>
+      <c r="G32" s="2">
+        <v>100</v>
+      </c>
+      <c r="H32" s="2">
+        <v>100</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>30</v>
@@ -3021,13 +2844,13 @@
         <v>16</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="O32" s="16"/>
       <c r="P32" s="16"/>
@@ -3054,7 +2877,7 @@
         <v>20</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>12</v>
@@ -3064,11 +2887,11 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>180</v>
+      <c r="G33" s="2">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2">
+        <v>30</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>30</v>
@@ -3080,13 +2903,13 @@
         <v>16</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>181</v>
+        <v>124</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
@@ -3113,7 +2936,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>21</v>
@@ -3122,14 +2945,14 @@
         <v>13</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>184</v>
+      <c r="F34" s="2">
+        <v>300</v>
+      </c>
+      <c r="G34" s="9">
+        <v>600</v>
+      </c>
+      <c r="H34" s="9">
+        <v>900</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>28</v>
@@ -3141,7 +2964,7 @@
         <v>16</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="9"/>
@@ -3170,7 +2993,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>21</v>
@@ -3180,11 +3003,11 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>187</v>
+      <c r="G35" s="28">
+        <v>1875</v>
+      </c>
+      <c r="H35" s="31">
+        <v>1875</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>25</v>
@@ -3196,13 +3019,13 @@
         <v>16</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="O35" s="16"/>
       <c r="P35" s="16"/>
@@ -3229,7 +3052,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>21</v>
@@ -3239,11 +3062,11 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>192</v>
+      <c r="G36" s="2">
+        <v>330</v>
+      </c>
+      <c r="H36" s="2">
+        <v>330</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>18</v>
@@ -3255,13 +3078,13 @@
         <v>16</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="M36" s="15" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="O36" s="16"/>
       <c r="P36" s="16"/>
@@ -3288,7 +3111,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>21</v>
@@ -3298,11 +3121,11 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>197</v>
+      <c r="G37" s="2">
+        <v>390</v>
+      </c>
+      <c r="H37" s="2">
+        <v>390</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>18</v>
@@ -3314,13 +3137,13 @@
         <v>16</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="M37" s="15" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="O37" s="16"/>
       <c r="P37" s="16"/>
@@ -3347,7 +3170,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>21</v>
@@ -3357,11 +3180,11 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>100</v>
+      <c r="G38" s="2">
+        <v>120</v>
+      </c>
+      <c r="H38" s="2">
+        <v>120</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>18</v>
@@ -3373,13 +3196,13 @@
         <v>16</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="M38" s="15" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="O38" s="16"/>
       <c r="P38" s="16"/>
@@ -3416,11 +3239,11 @@
       </c>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
-      <c r="G39" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>204</v>
+      <c r="G39" s="20">
+        <v>119</v>
+      </c>
+      <c r="H39" s="20">
+        <v>119</v>
       </c>
       <c r="I39" s="20" t="s">
         <v>18</v>
@@ -3432,13 +3255,13 @@
         <v>16</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>205</v>
+        <v>139</v>
       </c>
       <c r="M39" s="23" t="s">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39" s="16"/>
@@ -6332,6 +6155,78 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="K66:L66"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="K82:L82"/>
+    <mergeCell ref="K83:L83"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="K91:L91"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="K110:L110"/>
     <mergeCell ref="K118:L118"/>
     <mergeCell ref="K119:L119"/>
     <mergeCell ref="K120:L120"/>
@@ -6342,78 +6237,6 @@
     <mergeCell ref="K115:L115"/>
     <mergeCell ref="K116:L116"/>
     <mergeCell ref="K117:L117"/>
-    <mergeCell ref="K106:L106"/>
-    <mergeCell ref="K107:L107"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="K109:L109"/>
-    <mergeCell ref="K110:L110"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="K103:L103"/>
-    <mergeCell ref="K104:L104"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="K94:L94"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="K91:L91"/>
-    <mergeCell ref="K92:L92"/>
-    <mergeCell ref="K93:L93"/>
-    <mergeCell ref="K82:L82"/>
-    <mergeCell ref="K83:L83"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="K85:L85"/>
-    <mergeCell ref="K86:L86"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="K77:L77"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="K81:L81"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="K71:L71"/>
-    <mergeCell ref="K72:L72"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="K75:L75"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="K66:L66"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="K45:L45"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/helper_tools/Workload Seeder.xlsx
+++ b/helper_tools/Workload Seeder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/mohamed_mitkees_oracle_com/Documents/SalesAPP/helper_tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{CB7DE02C-0636-E94C-93FF-F9FC079531BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A0F74B-09A0-794C-8BE1-91ADE0433FA0}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CB7DE02C-0636-E94C-93FF-F9FC079531BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADA1DB73-9A10-0D42-8590-12A0AAC89DAE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>Start Date</t>
   </si>
   <si>
-    <t>COMMENTS</t>
-  </si>
-  <si>
     <t>Won</t>
   </si>
   <si>
@@ -464,6 +461,9 @@
   </si>
   <si>
     <t>They will expand their ops in UK.-Won 120/Month</t>
+  </si>
+  <si>
+    <t>Workload Details</t>
   </si>
 </sst>
 </file>
@@ -952,13 +952,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="G1" s="26" t="s">
         <v>142</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>143</v>
       </c>
       <c r="H1" s="26" t="s">
         <v>4</v>
@@ -979,10 +979,10 @@
         <v>9</v>
       </c>
       <c r="N1" s="26" t="s">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P1" s="18"/>
       <c r="Q1" s="18"/>
@@ -1005,22 +1005,22 @@
     </row>
     <row r="2" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="G2" s="28">
         <v>1000</v>
@@ -1029,22 +1029,22 @@
         <v>1000</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -1068,19 +1068,19 @@
     </row>
     <row r="3" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F3" s="2">
         <v>100</v>
@@ -1092,20 +1092,20 @@
         <v>200</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="K3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
@@ -1129,16 +1129,16 @@
     </row>
     <row r="4" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1149,20 +1149,20 @@
         <v>600</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="O4" s="16"/>
       <c r="P4" s="16"/>
@@ -1186,16 +1186,16 @@
     </row>
     <row r="5" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="2">
         <v>475</v>
@@ -1210,22 +1210,22 @@
         <v>1891</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
@@ -1249,16 +1249,16 @@
     </row>
     <row r="6" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1269,20 +1269,20 @@
         <v>2000</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
@@ -1306,19 +1306,19 @@
     </row>
     <row r="7" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F7" s="2">
         <v>824</v>
@@ -1330,22 +1330,22 @@
         <v>4214</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
@@ -1369,16 +1369,16 @@
     </row>
     <row r="8" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -1389,20 +1389,20 @@
         <v>1769</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M8" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="N8" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
@@ -1426,16 +1426,16 @@
     </row>
     <row r="9" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1446,20 +1446,20 @@
         <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
@@ -1483,16 +1483,16 @@
     </row>
     <row r="10" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="D10" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2">
@@ -1505,22 +1505,22 @@
         <v>1551</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="N10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
@@ -1544,19 +1544,19 @@
     </row>
     <row r="11" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F11" s="2">
         <v>850</v>
@@ -1568,20 +1568,20 @@
         <v>1700</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
@@ -1605,22 +1605,22 @@
     </row>
     <row r="12" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="G12" s="28">
         <v>1200</v>
@@ -1629,22 +1629,22 @@
         <v>1200</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="K12" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="M12" s="12" t="s">
-        <v>64</v>
-      </c>
       <c r="N12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O12" s="16"/>
       <c r="P12" s="16"/>
@@ -1668,16 +1668,16 @@
     </row>
     <row r="13" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
@@ -1690,22 +1690,22 @@
         <v>200</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="O13" s="16"/>
       <c r="P13" s="16"/>
@@ -1725,52 +1725,52 @@
       <c r="AD13" s="16"/>
       <c r="AE13" s="16"/>
       <c r="AF13" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG13" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2">
         <v>850</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H14" s="2">
         <v>850</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
@@ -1794,16 +1794,16 @@
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E15" s="28">
         <v>2000</v>
@@ -1818,20 +1818,20 @@
         <v>6000</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
@@ -1855,16 +1855,16 @@
     </row>
     <row r="16" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2">
         <v>120</v>
@@ -1879,22 +1879,22 @@
         <v>360</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="N16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
@@ -1918,16 +1918,16 @@
     </row>
     <row r="17" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="28">
@@ -1940,20 +1940,20 @@
         <v>2000</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="O17" s="16"/>
       <c r="P17" s="16"/>
@@ -1977,16 +1977,16 @@
     </row>
     <row r="18" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="28">
         <v>2500</v>
@@ -2001,20 +2001,20 @@
         <v>8500</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N18" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="O18" s="16"/>
       <c r="P18" s="16"/>
@@ -2029,13 +2029,13 @@
       <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
       <c r="AA18" s="16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB18" s="16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC18" s="16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD18" s="16"/>
       <c r="AE18" s="16"/>
@@ -2044,16 +2044,16 @@
     </row>
     <row r="19" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -2064,22 +2064,22 @@
         <v>1000</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="K19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="O19" s="24"/>
       <c r="P19" s="16"/>
@@ -2103,16 +2103,16 @@
     </row>
     <row r="20" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -2123,22 +2123,22 @@
         <v>840</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="O20" s="16"/>
       <c r="P20" s="16"/>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="21" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="28">
@@ -2182,16 +2182,16 @@
         <v>10000</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="L21" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M21" s="12"/>
       <c r="N21" s="2"/>
@@ -2217,19 +2217,19 @@
     </row>
     <row r="22" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2">
@@ -2239,20 +2239,20 @@
         <v>600</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M22" s="12"/>
       <c r="N22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
@@ -2276,16 +2276,16 @@
     </row>
     <row r="23" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="29">
@@ -2298,20 +2298,20 @@
         <v>3944</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>97</v>
       </c>
       <c r="M23" s="14"/>
       <c r="N23" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O23" s="16"/>
       <c r="P23" s="16"/>
@@ -2335,19 +2335,19 @@
     </row>
     <row r="24" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2">
@@ -2357,20 +2357,20 @@
         <v>500</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="O24" s="16"/>
       <c r="P24" s="16"/>
@@ -2394,16 +2394,16 @@
     </row>
     <row r="25" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="2">
         <v>300</v>
@@ -2414,22 +2414,22 @@
         <v>300</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
@@ -2453,16 +2453,16 @@
     </row>
     <row r="26" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -2473,19 +2473,19 @@
         <v>50</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L26" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="24"/>
@@ -2510,16 +2510,16 @@
     </row>
     <row r="27" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="28">
         <v>1000</v>
@@ -2534,20 +2534,20 @@
         <v>3200</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="O27" s="16"/>
       <c r="P27" s="16"/>
@@ -2567,24 +2567,24 @@
       <c r="AD27" s="16"/>
       <c r="AE27" s="16"/>
       <c r="AF27" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG27" s="16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>12</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -2595,22 +2595,22 @@
         <v>1100</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K28" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="L28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N28" s="9" t="s">
         <v>108</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N28" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="O28" s="24"/>
       <c r="P28" s="16"/>
@@ -2634,46 +2634,46 @@
     </row>
     <row r="29" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="28">
         <v>3300</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H29" s="30">
         <v>3300</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="L29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
@@ -2697,16 +2697,16 @@
     </row>
     <row r="30" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="28">
         <v>1600</v>
@@ -2717,20 +2717,20 @@
         <v>1600</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
@@ -2754,16 +2754,16 @@
     </row>
     <row r="31" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E31" s="28">
         <v>1000</v>
@@ -2778,20 +2778,20 @@
         <v>4000</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="N31" s="16" t="s">
         <v>118</v>
-      </c>
-      <c r="N31" s="16" t="s">
-        <v>119</v>
       </c>
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
@@ -2815,16 +2815,16 @@
     </row>
     <row r="32" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2835,22 +2835,22 @@
         <v>100</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N32" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="O32" s="16"/>
       <c r="P32" s="16"/>
@@ -2874,16 +2874,16 @@
     </row>
     <row r="33" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2894,22 +2894,22 @@
         <v>30</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L33" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N33" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
@@ -2933,16 +2933,16 @@
     </row>
     <row r="34" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2">
@@ -2955,16 +2955,16 @@
         <v>900</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="9"/>
@@ -2990,16 +2990,16 @@
     </row>
     <row r="35" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -3010,22 +3010,22 @@
         <v>1875</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L35" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="M35" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="O35" s="16"/>
       <c r="P35" s="16"/>
@@ -3049,16 +3049,16 @@
     </row>
     <row r="36" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -3069,22 +3069,22 @@
         <v>330</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L36" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="N36" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="O36" s="16"/>
       <c r="P36" s="16"/>
@@ -3108,16 +3108,16 @@
     </row>
     <row r="37" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -3128,22 +3128,22 @@
         <v>390</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L37" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="M37" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="M37" s="15" t="s">
-        <v>135</v>
-      </c>
       <c r="N37" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O37" s="16"/>
       <c r="P37" s="16"/>
@@ -3167,16 +3167,16 @@
     </row>
     <row r="38" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -3187,22 +3187,22 @@
         <v>120</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L38" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="M38" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="M38" s="15" t="s">
-        <v>138</v>
-      </c>
       <c r="N38" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O38" s="16"/>
       <c r="P38" s="16"/>
@@ -3226,16 +3226,16 @@
     </row>
     <row r="39" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
@@ -3246,22 +3246,22 @@
         <v>119</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J39" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K39" s="22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L39" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="M39" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="M39" s="23" t="s">
-        <v>140</v>
-      </c>
       <c r="N39" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39" s="16"/>
